--- a/artfynd/A 57970-2022 artfynd.xlsx
+++ b/artfynd/A 57970-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131737121</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131738253</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131732314</v>
+        <v>131738252</v>
       </c>
       <c r="B4" t="n">
-        <v>83161</v>
+        <v>80422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585185</v>
+        <v>585287</v>
       </c>
       <c r="R4" t="n">
-        <v>6898434</v>
+        <v>6898424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131738252</v>
+        <v>131732314</v>
       </c>
       <c r="B5" t="n">
-        <v>80420</v>
+        <v>83163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585287</v>
+        <v>585185</v>
       </c>
       <c r="R5" t="n">
-        <v>6898424</v>
+        <v>6898434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131740591</v>
+        <v>131734600</v>
       </c>
       <c r="B6" t="n">
-        <v>106204</v>
+        <v>80382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
         <v>585291</v>
       </c>
       <c r="R6" t="n">
-        <v>6898436</v>
+        <v>6898425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131734600</v>
+        <v>131740591</v>
       </c>
       <c r="B7" t="n">
-        <v>80380</v>
+        <v>106207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>585291</v>
       </c>
       <c r="R7" t="n">
-        <v>6898425</v>
+        <v>6898436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>131734245</v>
       </c>
       <c r="B8" t="n">
-        <v>80456</v>
+        <v>80458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>131740324</v>
       </c>
       <c r="B9" t="n">
-        <v>92849</v>
+        <v>92852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131734246</v>
+        <v>131738251</v>
       </c>
       <c r="B10" t="n">
-        <v>80456</v>
+        <v>80422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585330</v>
+        <v>585289</v>
       </c>
       <c r="R10" t="n">
-        <v>6898421</v>
+        <v>6898423</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131738251</v>
+        <v>131734246</v>
       </c>
       <c r="B11" t="n">
-        <v>80420</v>
+        <v>80458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585289</v>
+        <v>585330</v>
       </c>
       <c r="R11" t="n">
-        <v>6898423</v>
+        <v>6898421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
         <v>131738254</v>
       </c>
       <c r="B12" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131734601</v>
+        <v>131734244</v>
       </c>
       <c r="B13" t="n">
-        <v>80380</v>
+        <v>80458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585329</v>
+        <v>585290</v>
       </c>
       <c r="R13" t="n">
-        <v>6898424</v>
+        <v>6898423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131734244</v>
+        <v>131734601</v>
       </c>
       <c r="B14" t="n">
-        <v>80456</v>
+        <v>80382</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585290</v>
+        <v>585329</v>
       </c>
       <c r="R14" t="n">
-        <v>6898423</v>
+        <v>6898424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 57970-2022 artfynd.xlsx
+++ b/artfynd/A 57970-2022 artfynd.xlsx
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131738251</v>
+        <v>131734246</v>
       </c>
       <c r="B10" t="n">
-        <v>80422</v>
+        <v>80458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585289</v>
+        <v>585330</v>
       </c>
       <c r="R10" t="n">
-        <v>6898423</v>
+        <v>6898421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131734246</v>
+        <v>131738251</v>
       </c>
       <c r="B11" t="n">
-        <v>80458</v>
+        <v>80422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585330</v>
+        <v>585289</v>
       </c>
       <c r="R11" t="n">
-        <v>6898421</v>
+        <v>6898423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 57970-2022 artfynd.xlsx
+++ b/artfynd/A 57970-2022 artfynd.xlsx
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131734246</v>
+        <v>131738251</v>
       </c>
       <c r="B10" t="n">
-        <v>80458</v>
+        <v>80422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585330</v>
+        <v>585289</v>
       </c>
       <c r="R10" t="n">
-        <v>6898421</v>
+        <v>6898423</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131738251</v>
+        <v>131734246</v>
       </c>
       <c r="B11" t="n">
-        <v>80422</v>
+        <v>80458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585289</v>
+        <v>585330</v>
       </c>
       <c r="R11" t="n">
-        <v>6898423</v>
+        <v>6898421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 57970-2022 artfynd.xlsx
+++ b/artfynd/A 57970-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131737121</v>
       </c>
       <c r="B2" t="n">
-        <v>92191</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131738253</v>
+        <v>131732314</v>
       </c>
       <c r="B3" t="n">
-        <v>80422</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585331</v>
+        <v>585185</v>
       </c>
       <c r="R3" t="n">
-        <v>6898423</v>
+        <v>6898434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131738252</v>
+        <v>131737547</v>
       </c>
       <c r="B4" t="n">
-        <v>80422</v>
+        <v>96413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585287</v>
+        <v>585142</v>
       </c>
       <c r="R4" t="n">
-        <v>6898424</v>
+        <v>6898434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131732314</v>
+        <v>131740324</v>
       </c>
       <c r="B5" t="n">
-        <v>83163</v>
+        <v>92943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585185</v>
+        <v>585320</v>
       </c>
       <c r="R5" t="n">
-        <v>6898434</v>
+        <v>6898447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131734600</v>
+        <v>131738251</v>
       </c>
       <c r="B6" t="n">
-        <v>80382</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585291</v>
+        <v>585289</v>
       </c>
       <c r="R6" t="n">
-        <v>6898425</v>
+        <v>6898423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131740591</v>
+        <v>131738252</v>
       </c>
       <c r="B7" t="n">
-        <v>106207</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585291</v>
+        <v>585287</v>
       </c>
       <c r="R7" t="n">
-        <v>6898436</v>
+        <v>6898424</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131734245</v>
+        <v>131738253</v>
       </c>
       <c r="B8" t="n">
-        <v>80458</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585287</v>
+        <v>585331</v>
       </c>
       <c r="R8" t="n">
-        <v>6898424</v>
+        <v>6898423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131740324</v>
+        <v>131738254</v>
       </c>
       <c r="B9" t="n">
-        <v>92852</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585320</v>
+        <v>585300</v>
       </c>
       <c r="R9" t="n">
-        <v>6898447</v>
+        <v>6898441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1453,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg. Dålig bål.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131738251</v>
+        <v>131734244</v>
       </c>
       <c r="B10" t="n">
-        <v>80422</v>
+        <v>80500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,7 +1523,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585289</v>
+        <v>585290</v>
       </c>
       <c r="R10" t="n">
         <v>6898423</v>
@@ -1584,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131734246</v>
+        <v>131734245</v>
       </c>
       <c r="B11" t="n">
-        <v>80458</v>
+        <v>80500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585330</v>
+        <v>585287</v>
       </c>
       <c r="R11" t="n">
-        <v>6898421</v>
+        <v>6898424</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131738254</v>
+        <v>131734246</v>
       </c>
       <c r="B12" t="n">
-        <v>80422</v>
+        <v>80500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585300</v>
+        <v>585330</v>
       </c>
       <c r="R12" t="n">
-        <v>6898441</v>
+        <v>6898421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1761,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälg. Dålig bål.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131734244</v>
+        <v>131734345</v>
       </c>
       <c r="B13" t="n">
-        <v>80458</v>
+        <v>108274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>220102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585290</v>
+        <v>585300</v>
       </c>
       <c r="R13" t="n">
-        <v>6898423</v>
+        <v>6898443</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131734601</v>
+        <v>131740005</v>
       </c>
       <c r="B14" t="n">
-        <v>80382</v>
+        <v>109924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>221184</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585329</v>
+        <v>585323</v>
       </c>
       <c r="R14" t="n">
-        <v>6898424</v>
+        <v>6898437</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,6 +1986,410 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131740591</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klövbergets naturreservat Öst, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585291</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6898436</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131734599</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klövbergets naturreservat Öst, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585287</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6898421</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131734600</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klövbergets naturreservat Öst, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585291</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6898425</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131734601</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klövbergets naturreservat Öst, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585329</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6898424</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hassela</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 57970-2022 artfynd.xlsx
+++ b/artfynd/A 57970-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737121</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737547</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740324</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738251</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738252</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738253</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734244</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734245</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734246</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734345</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740005</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740591</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734599</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,8 +2479,32 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>